--- a/rwa-with-ui/Backend/data/Main Data.xlsx
+++ b/rwa-with-ui/Backend/data/Main Data.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="om_cdm_rwa_mtrc" sheetId="1" r:id="Re64f5b32cb944e89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="om_cdm_rwa_mtrc_extn" sheetId="2" r:id="Rc8c36ad5f3be4856"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dsft_conc_txn_result" sheetId="3" r:id="R36ca7d137e3b4bb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dsft_conc_result_txn_map" sheetId="4" r:id="R318ef6cd26d84234"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dsft_conc_result" sheetId="5" r:id="Rc4c7579a1b2d4a98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dsft_fi_base_subassetclass" sheetId="6" r:id="Rc33ce320852c48e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="om_cdm_rwa_mtrc" sheetId="1" r:id="R5f883bc1b77245eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="om_cdm_rwa_mtrc_extn" sheetId="2" r:id="R536c5097db4c40cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dsft_conc_txn_result" sheetId="3" r:id="Rc68b52d5347d494e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dsft_conc_result_txn_map" sheetId="4" r:id="R7ceb10505db14661"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dsft_conc_result" sheetId="5" r:id="R675c21a8d2234b37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dsft_fi_base_subassetclass" sheetId="6" r:id="R734311960d7449aa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -794,22 +794,22 @@
         <x:v>1123456918</x:v>
       </x:c>
       <x:c r="B3" s="47" t="str">
-        <x:v>78462A1K3</x:v>
+        <x:v>4917989V8</x:v>
       </x:c>
       <x:c r="C3" s="47" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D3" s="56" t="n">
-        <x:v>810000</x:v>
+        <x:v>1150000</x:v>
       </x:c>
       <x:c r="E3" s="47" t="str">
         <x:v>B</x:v>
       </x:c>
       <x:c r="F3" s="47" t="n">
-        <x:v>2123783</x:v>
+        <x:v>2123999</x:v>
       </x:c>
       <x:c r="G3" s="47" t="str">
-        <x:v>202505208123456SN6</x:v>
+        <x:v>202505198123456SN5</x:v>
       </x:c>
       <x:c r="H3" s="47" t="str">
         <x:v>Y</x:v>
@@ -817,28 +817,28 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="47" t="n">
-        <x:v>1123456567</x:v>
+        <x:v>1123456918</x:v>
       </x:c>
       <x:c r="B4" s="47" t="str">
-        <x:v>6G061567B</x:v>
+        <x:v>78462A1K3</x:v>
       </x:c>
       <x:c r="C4" s="47" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D4" s="56" t="n">
-        <x:v>8830003.084</x:v>
+        <x:v>810000</x:v>
       </x:c>
       <x:c r="E4" s="47" t="str">
         <x:v>B</x:v>
       </x:c>
       <x:c r="F4" s="47" t="n">
-        <x:v>2253783</x:v>
+        <x:v>2123783</x:v>
       </x:c>
       <x:c r="G4" s="47" t="str">
-        <x:v>202501978123456SN5</x:v>
+        <x:v>202505208123456SN6</x:v>
       </x:c>
       <x:c r="H4" s="47" t="str">
-        <x:v>N</x:v>
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -846,13 +846,13 @@
         <x:v>1123456567</x:v>
       </x:c>
       <x:c r="B5" s="47" t="str">
-        <x:v>9N2026PZ4</x:v>
+        <x:v>6G061567B</x:v>
       </x:c>
       <x:c r="C5" s="47" t="n">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D5" s="56" t="n">
-        <x:v>2210000</x:v>
+        <x:v>8830003.084</x:v>
       </x:c>
       <x:c r="E5" s="47" t="str">
         <x:v>B</x:v>
@@ -861,21 +861,37 @@
         <x:v>2253783</x:v>
       </x:c>
       <x:c r="G5" s="47" t="str">
+        <x:v>202501978123456SN5</x:v>
+      </x:c>
+      <x:c r="H5" s="47" t="str">
+        <x:v>N</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="47" t="n">
+        <x:v>1123456567</x:v>
+      </x:c>
+      <x:c r="B6" s="47" t="str">
+        <x:v>9N2026PZ4</x:v>
+      </x:c>
+      <x:c r="C6" s="47" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D6" s="56" t="n">
+        <x:v>2210000</x:v>
+      </x:c>
+      <x:c r="E6" s="47" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="F6" s="47" t="n">
+        <x:v>2253783</x:v>
+      </x:c>
+      <x:c r="G6" s="47" t="str">
         <x:v>202502018123456SN6</x:v>
       </x:c>
-      <x:c r="H5" s="47" t="str">
+      <x:c r="H6" s="47" t="str">
         <x:v>Y</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="41"/>
-      <x:c r="B6" s="41"/>
-      <x:c r="C6" s="41"/>
-      <x:c r="D6" s="42"/>
-      <x:c r="E6" s="41"/>
-      <x:c r="F6" s="41"/>
-      <x:c r="G6" s="41"/>
-      <x:c r="H6" s="41"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="41"/>
